--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/DISTRICT_OF_COLUMBIA_2015.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2015/DISTRICT_OF_COLUMBIA_2015.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -428,7 +438,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C5">
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Simojovel</t>
@@ -517,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Socoltenango</t>
@@ -530,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -543,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -556,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -569,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -582,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -595,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -698,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -753,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C29">
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -901,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -914,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -929,7 +1099,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -945,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C43">
@@ -958,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -971,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C45">
@@ -984,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -997,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1023,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C49">
@@ -1036,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -1049,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1062,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Valle de Bravo</t>
+          <t>Valle De Bravo</t>
         </is>
       </c>
       <c r="C52">
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1095,7 +1320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C54">
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -1132,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C57">
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>León</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1217,7 +1482,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C63">
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1241,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C65">
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -1267,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C67">
@@ -1280,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -1293,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C69">
@@ -1306,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C70">
@@ -1319,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C71">
@@ -1332,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1345,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1358,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C74">
@@ -1371,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C75">
@@ -1384,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -1397,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -1410,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tixtla de Guerrero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C78">
@@ -1423,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C79">
@@ -1436,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -1449,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1462,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Apan</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>San Agustín Tlaxiaca</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>San Salvador</t>
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1576,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1589,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Huejuquilla el Alto</t>
+          <t>Huejuquilla El Alto</t>
         </is>
       </c>
       <c r="C91">
@@ -1602,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -1615,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1628,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1641,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1672,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -1685,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -1698,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -1711,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1724,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1737,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1768,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -1781,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1794,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1825,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1856,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C110">
@@ -1869,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C111">
@@ -1882,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Coatecas Altas</t>
@@ -1895,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Coicoyán de las Flores</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C113">
@@ -1908,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -1921,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Guadalupe Etla</t>
@@ -1934,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C116">
@@ -1947,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C117">
@@ -1960,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C118">
@@ -1973,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -1986,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Magdalena Apasco</t>
@@ -1999,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Magdalena Tequisistlán</t>
@@ -2012,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C122">
@@ -2025,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C123">
@@ -2038,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C124">
@@ -2051,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>San Francisco Ixhuatán</t>
@@ -2064,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>San Juan Bautista Cuicatlán</t>
@@ -2077,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>San Juan Bautista Guelache</t>
@@ -2090,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>San Juan Bautista Jayacatlán</t>
@@ -2103,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -2116,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>San Juan Bautista Valle Nacional</t>
@@ -2129,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>San Juan Mixtepec - Distr. 08 -</t>
@@ -2142,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>San Juan Ozolotepec</t>
@@ -2155,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>San Miguel Huautla</t>
@@ -2168,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -2181,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -2194,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>San Sebastián Tecomaxtlahuaca</t>
@@ -2207,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -2220,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Santo Domingo de Morelos</t>
+          <t>Santo Domingo De Morelos</t>
         </is>
       </c>
       <c r="C138">
@@ -2233,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Santo Tomás Mazaltepec</t>
@@ -2246,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -2259,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -2272,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C142">
@@ -2285,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Villa de Chilapa de Díaz</t>
+          <t>Villa De Chilapa De Díaz</t>
         </is>
       </c>
       <c r="C143">
@@ -2298,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C144">
@@ -2311,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2342,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -2355,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -2368,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -2381,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -2394,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C151">
@@ -2407,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>General Felipe Ángeles</t>
@@ -2420,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -2433,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Hueytamalco</t>
@@ -2446,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C155">
@@ -2459,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Mixtla</t>
@@ -2472,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -2485,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -2498,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Petlalcingo</t>
@@ -2511,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2524,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -2537,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -2550,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -2563,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>San Gabriel Chilac</t>
@@ -2576,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -2589,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -2602,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Tecomatlán</t>
@@ -2615,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -2628,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -2641,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Teotlalco</t>
@@ -2654,9 +3419,14 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C171">
@@ -2667,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -2680,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C173">
@@ -2693,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -2706,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -2719,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Xiutetelco</t>
@@ -2732,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -2745,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -2758,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2778,7 +3588,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C180">
@@ -2789,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C181">
@@ -2802,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -2815,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2846,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2877,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2908,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -2921,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2952,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2983,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -2996,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -3009,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>San José Teacalco</t>
@@ -3022,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -3035,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3048,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Yauhquemehcan</t>
@@ -3061,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3092,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C202">
@@ -3105,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Atzalan</t>
@@ -3118,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -3131,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -3144,9 +4049,14 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C206">
@@ -3157,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Fortín</t>
@@ -3170,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -3183,9 +4103,14 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C209">
@@ -3196,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Mecayapan</t>
@@ -3209,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -3222,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Paso del Macho</t>
+          <t>Paso Del Macho</t>
         </is>
       </c>
       <c r="C212">
@@ -3235,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -3248,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -3261,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -3274,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -3287,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -3300,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -3313,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -3326,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -3339,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Yecuatla</t>
@@ -3352,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3383,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Tixkokob</t>
@@ -3396,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3427,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C227">
@@ -3440,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -3453,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3476,41 +4491,6 @@
       </c>
       <c r="D230">
         <v>1</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
